--- a/salidas/empresas/AIG.xlsx
+++ b/salidas/empresas/AIG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>774.8092041015625</v>
+        <v>774.8095092773438</v>
       </c>
       <c r="C2" t="n">
         <v>1309.199951171875</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>785.4617919921875</v>
+        <v>785.4620971679688</v>
       </c>
       <c r="C3" t="n">
         <v>1327.199951171875</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>784.0386352539062</v>
+        <v>784.0383911132812</v>
       </c>
       <c r="C4" t="n">
         <v>1321.800048828125</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>774.0733032226562</v>
+        <v>774.0734252929688</v>
       </c>
       <c r="C5" t="n">
         <v>1305</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>723.0718383789062</v>
+        <v>723.0718994140625</v>
       </c>
       <c r="C6" t="n">
         <v>1216</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>702.2597045898438</v>
+        <v>702.2599487304688</v>
       </c>
       <c r="C7" t="n">
         <v>1181</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>721.5258178710938</v>
+        <v>721.5256958007812</v>
       </c>
       <c r="C8" t="n">
         <v>1213.400024414062</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>760.9619750976562</v>
+        <v>760.961669921875</v>
       </c>
       <c r="C9" t="n">
         <v>1276.400024414062</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>790.0553588867188</v>
+        <v>790.0552368164062</v>
       </c>
       <c r="C10" t="n">
         <v>1325.199951171875</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>800.906005859375</v>
+        <v>800.9056396484375</v>
       </c>
       <c r="C11" t="n">
         <v>1343.400024414062</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>856.4656982421875</v>
+        <v>856.4657592773438</v>
       </c>
       <c r="C13" t="n">
         <v>1433.199951171875</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>818.1002197265625</v>
+        <v>818.1004028320312</v>
       </c>
       <c r="C14" t="n">
         <v>1369</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>805.389892578125</v>
+        <v>805.3901977539062</v>
       </c>
       <c r="C16" t="n">
         <v>1344.400024414062</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>837.6199951171875</v>
+        <v>837.6201171875</v>
       </c>
       <c r="C17" t="n">
         <v>1398.199951171875</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>868.728515625</v>
+        <v>868.7284545898438</v>
       </c>
       <c r="C18" t="n">
         <v>1446.800048828125</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>840.9880981445312</v>
+        <v>840.9876098632812</v>
       </c>
       <c r="C19" t="n">
         <v>1400.599975585938</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>792.5919799804688</v>
+        <v>792.5914306640625</v>
       </c>
       <c r="C21" t="n">
         <v>1320</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>760.2908325195312</v>
+        <v>760.2904052734375</v>
       </c>
       <c r="C23" t="n">
         <v>1262.400024414062</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>700.1849975585938</v>
+        <v>700.1852416992188</v>
       </c>
       <c r="C24" t="n">
         <v>1162.599975585938</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>704.7655029296875</v>
+        <v>704.7655639648438</v>
       </c>
       <c r="C25" t="n">
         <v>1166</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>664.5106811523438</v>
+        <v>664.5106201171875</v>
       </c>
       <c r="C26" t="n">
         <v>1099.400024414062</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>525.1238403320312</v>
+        <v>525.1239624023438</v>
       </c>
       <c r="C28" t="n">
         <v>865</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>560.9412841796875</v>
+        <v>560.9415893554688</v>
       </c>
       <c r="C29" t="n">
         <v>924</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>437.0972595214844</v>
+        <v>437.0973205566406</v>
       </c>
       <c r="C30" t="n">
         <v>720</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>262.3800659179688</v>
+        <v>262.3800354003906</v>
       </c>
       <c r="C33" t="n">
         <v>429.7999877929688</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.06874465942383</v>
+        <v>41.06874084472656</v>
       </c>
       <c r="C34" t="n">
         <v>66.59999847412109</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>23.55594062805176</v>
+        <v>23.55594253540039</v>
       </c>
       <c r="C35" t="n">
         <v>38.20000076293945</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>24.78923988342285</v>
+        <v>24.78923797607422</v>
       </c>
       <c r="C36" t="n">
         <v>40.20000076293945</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>19.36273956298828</v>
+        <v>19.36274147033691</v>
       </c>
       <c r="C37" t="n">
         <v>31.39999961853027</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.78618717193604</v>
+        <v>15.78617858886719</v>
       </c>
       <c r="C38" t="n">
         <v>25.60000038146973</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.179842472076416</v>
+        <v>5.179841041564941</v>
       </c>
       <c r="C39" t="n">
         <v>8.399999618530273</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.33295726776123</v>
+        <v>12.3329553604126</v>
       </c>
       <c r="C40" t="n">
         <v>20</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>17.01947975158691</v>
+        <v>17.01948165893555</v>
       </c>
       <c r="C41" t="n">
         <v>27.60000038146973</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.84269905090332</v>
+        <v>20.84269523620605</v>
       </c>
       <c r="C42" t="n">
         <v>33.79999923706055</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.30623340606689</v>
+        <v>14.30622959136963</v>
       </c>
       <c r="C43" t="n">
         <v>23.20000076293945</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>8.102749824523926</v>
+        <v>8.102753639221191</v>
       </c>
       <c r="C44" t="n">
         <v>13.14000034332275</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>27.9526481628418</v>
+        <v>27.95264434814453</v>
       </c>
       <c r="C45" t="n">
         <v>45.33000183105469</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>27.20032501220703</v>
+        <v>27.2003345489502</v>
       </c>
       <c r="C46" t="n">
         <v>44.11000061035156</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>20.73170280456543</v>
+        <v>20.7316951751709</v>
       </c>
       <c r="C47" t="n">
         <v>33.61999893188477</v>
@@ -1368,7 +1380,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.94137859344482</v>
+        <v>14.94138145446777</v>
       </c>
       <c r="C50" t="n">
         <v>24.22999954223633</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.27436923980713</v>
+        <v>15.27436351776123</v>
       </c>
       <c r="C51" t="n">
         <v>24.77000045776367</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.05235481262207</v>
+        <v>21.0523509979248</v>
       </c>
       <c r="C52" t="n">
         <v>34.13999938964844</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.98760223388672</v>
+        <v>23.98760032653809</v>
       </c>
       <c r="C53" t="n">
         <v>38.90000152587891</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>21.81700134277344</v>
+        <v>21.8169994354248</v>
       </c>
       <c r="C54" t="n">
         <v>35.38000106811523</v>
@@ -1543,7 +1555,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.72244453430176</v>
+        <v>23.72244071960449</v>
       </c>
       <c r="C56" t="n">
         <v>38.47000122070312</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>20.92285919189453</v>
+        <v>20.9228630065918</v>
       </c>
       <c r="C57" t="n">
         <v>33.93000030517578</v>
@@ -1618,7 +1630,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>25.90537452697754</v>
+        <v>25.9053783416748</v>
       </c>
       <c r="C59" t="n">
         <v>42.0099983215332</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>25.46138572692871</v>
+        <v>25.46138191223145</v>
       </c>
       <c r="C60" t="n">
         <v>41.29000091552734</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>35.53123474121094</v>
+        <v>35.53125</v>
       </c>
       <c r="C61" t="n">
         <v>57.61999893188477</v>
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>29.9968376159668</v>
+        <v>29.99683570861816</v>
       </c>
       <c r="C62" t="n">
         <v>40.34999847412109</v>
@@ -1743,7 +1755,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1772,11 +1784,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>26.12364387512207</v>
+        <v>26.1236457824707</v>
       </c>
       <c r="C64" t="n">
         <v>35.13999938964844</v>
@@ -1801,11 +1813,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>23.15741348266602</v>
+        <v>23.15740394592285</v>
       </c>
       <c r="C65" t="n">
         <v>31.14999961853027</v>
@@ -1830,11 +1842,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>21.18735504150391</v>
+        <v>21.18736267089844</v>
       </c>
       <c r="C66" t="n">
         <v>28.5</v>
@@ -1859,11 +1871,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.79695510864258</v>
+        <v>21.79696655273438</v>
       </c>
       <c r="C67" t="n">
         <v>29.31999969482422</v>
@@ -1888,11 +1900,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.33604621887207</v>
+        <v>21.33604049682617</v>
       </c>
       <c r="C68" t="n">
         <v>28.70000076293945</v>
@@ -1917,11 +1929,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>18.83072471618652</v>
+        <v>18.83073234558105</v>
       </c>
       <c r="C69" t="n">
         <v>25.32999992370605</v>
@@ -1946,11 +1958,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>16.31798362731934</v>
+        <v>16.3179874420166</v>
       </c>
       <c r="C70" t="n">
         <v>21.95000076293945</v>
@@ -1975,11 +1987,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>18.35494232177734</v>
+        <v>18.35495185852051</v>
       </c>
       <c r="C71" t="n">
         <v>24.69000053405762</v>
@@ -2004,11 +2016,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.32902908325195</v>
+        <v>17.32903099060059</v>
       </c>
       <c r="C72" t="n">
         <v>23.30999946594238</v>
@@ -2033,11 +2045,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.24725341796875</v>
+        <v>17.24725151062012</v>
       </c>
       <c r="C73" t="n">
         <v>23.20000076293945</v>
@@ -2062,11 +2074,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>18.66718101501465</v>
+        <v>18.66717910766602</v>
       </c>
       <c r="C74" t="n">
         <v>25.11000061035156</v>
@@ -2091,11 +2103,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.72261619567871</v>
+        <v>21.72261238098145</v>
       </c>
       <c r="C75" t="n">
         <v>29.21999931335449</v>
@@ -2120,11 +2132,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.91951560974121</v>
+        <v>22.91951942443848</v>
       </c>
       <c r="C76" t="n">
         <v>30.82999992370605</v>
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>25.29845237731934</v>
+        <v>25.29844856262207</v>
       </c>
       <c r="C77" t="n">
         <v>34.02999877929688</v>
@@ -2178,11 +2190,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>21.69288444519043</v>
+        <v>21.69288063049316</v>
       </c>
       <c r="C78" t="n">
         <v>29.18000030517578</v>
@@ -2207,11 +2219,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>23.85622406005859</v>
+        <v>23.85622024536133</v>
       </c>
       <c r="C79" t="n">
         <v>32.09000015258789</v>
@@ -2236,11 +2248,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>23.24662017822266</v>
+        <v>23.24662399291992</v>
       </c>
       <c r="C80" t="n">
         <v>31.27000045776367</v>
@@ -2265,11 +2277,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.52148246765137</v>
+        <v>25.52147674560547</v>
       </c>
       <c r="C81" t="n">
         <v>34.33000183105469</v>
@@ -2294,11 +2306,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.37661552429199</v>
+        <v>24.37662124633789</v>
       </c>
       <c r="C82" t="n">
         <v>32.79000091552734</v>
@@ -2323,11 +2335,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.96752548217773</v>
+        <v>25.9675235748291</v>
       </c>
       <c r="C83" t="n">
         <v>34.93000030517578</v>
@@ -2352,11 +2364,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>24.62937545776367</v>
+        <v>24.6293773651123</v>
       </c>
       <c r="C84" t="n">
         <v>33.13000106811523</v>
@@ -2381,11 +2393,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>26.24258422851562</v>
+        <v>26.24258613586426</v>
       </c>
       <c r="C85" t="n">
         <v>35.29999923706055</v>
@@ -2410,11 +2422,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>28.12343978881836</v>
+        <v>28.12344169616699</v>
       </c>
       <c r="C86" t="n">
         <v>37.83000183105469</v>
@@ -2439,11 +2451,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.25724411010742</v>
+        <v>28.25724601745605</v>
       </c>
       <c r="C87" t="n">
         <v>38.0099983215332</v>
@@ -2468,11 +2480,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>28.85941696166992</v>
+        <v>28.85940551757812</v>
       </c>
       <c r="C88" t="n">
         <v>38.81999969482422</v>
@@ -2497,7 +2509,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>33.05227661132812</v>
+        <v>33.05228042602539</v>
       </c>
       <c r="C90" t="n">
         <v>44.45999908447266</v>
@@ -2555,11 +2567,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>33.23070907592773</v>
+        <v>33.23070526123047</v>
       </c>
       <c r="C91" t="n">
         <v>44.70000076293945</v>
@@ -2584,11 +2596,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>33.83288192749023</v>
+        <v>33.83287048339844</v>
       </c>
       <c r="C92" t="n">
         <v>45.5099983215332</v>
@@ -2613,11 +2625,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>34.53912353515625</v>
+        <v>34.53911590576172</v>
       </c>
       <c r="C93" t="n">
         <v>46.45999908447266</v>
@@ -2642,7 +2654,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2671,11 +2683,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>38.47566223144531</v>
+        <v>38.47566604614258</v>
       </c>
       <c r="C95" t="n">
         <v>51.65000152587891</v>
@@ -2700,11 +2712,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>37.06029891967773</v>
+        <v>37.0602912902832</v>
       </c>
       <c r="C96" t="n">
         <v>49.75</v>
@@ -2729,11 +2741,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>38.1053581237793</v>
+        <v>38.10535049438477</v>
       </c>
       <c r="C97" t="n">
         <v>51.04999923706055</v>
@@ -2758,11 +2770,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>35.79888534545898</v>
+        <v>35.79889297485352</v>
       </c>
       <c r="C98" t="n">
         <v>47.95999908447266</v>
@@ -2787,7 +2799,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2816,11 +2828,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>37.42031860351562</v>
+        <v>37.42032241821289</v>
       </c>
       <c r="C100" t="n">
         <v>50.0099983215332</v>
@@ -2845,11 +2857,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>39.75488662719727</v>
+        <v>39.75486755371094</v>
       </c>
       <c r="C101" t="n">
         <v>53.13000106811523</v>
@@ -2874,11 +2886,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>40.4582405090332</v>
+        <v>40.45823287963867</v>
       </c>
       <c r="C102" t="n">
         <v>54.06999969482422</v>
@@ -2903,7 +2915,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2932,11 +2944,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>38.98306274414062</v>
+        <v>38.98306655883789</v>
       </c>
       <c r="C104" t="n">
         <v>51.97999954223633</v>
@@ -2961,11 +2973,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>42.04290390014648</v>
+        <v>42.04293060302734</v>
       </c>
       <c r="C105" t="n">
         <v>56.06000137329102</v>
@@ -2990,11 +3002,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>40.604736328125</v>
+        <v>40.60473251342773</v>
       </c>
       <c r="C106" t="n">
         <v>54.02000045776367</v>
@@ -3019,11 +3031,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>40.26648712158203</v>
+        <v>40.2664794921875</v>
       </c>
       <c r="C107" t="n">
         <v>53.56999969482422</v>
@@ -3048,7 +3060,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3077,11 +3089,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>42.19743728637695</v>
+        <v>42.19745635986328</v>
       </c>
       <c r="C109" t="n">
         <v>56.0099983215332</v>
@@ -3106,11 +3118,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>36.81824111938477</v>
+        <v>36.81822204589844</v>
       </c>
       <c r="C110" t="n">
         <v>48.86999893188477</v>
@@ -3135,7 +3147,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3164,11 +3176,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.3704719543457</v>
+        <v>41.37049865722656</v>
       </c>
       <c r="C112" t="n">
         <v>54.79000091552734</v>
@@ -3193,11 +3205,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>42.50308609008789</v>
+        <v>42.50308227539062</v>
       </c>
       <c r="C113" t="n">
         <v>56.29000091552734</v>
@@ -3222,11 +3234,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>44.25486373901367</v>
+        <v>44.25485610961914</v>
       </c>
       <c r="C114" t="n">
         <v>58.61000061035156</v>
@@ -3251,11 +3263,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>46.77665328979492</v>
+        <v>46.77665710449219</v>
       </c>
       <c r="C115" t="n">
         <v>61.81999969482422</v>
@@ -3280,11 +3292,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>48.51697540283203</v>
+        <v>48.51697158813477</v>
       </c>
       <c r="C116" t="n">
         <v>64.12000274658203</v>
@@ -3309,7 +3321,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3338,11 +3350,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>43.20001220703125</v>
+        <v>43.20002365112305</v>
       </c>
       <c r="C118" t="n">
         <v>56.81999969482422</v>
@@ -3367,11 +3379,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>47.94426727294922</v>
+        <v>47.94426345825195</v>
       </c>
       <c r="C119" t="n">
         <v>63.06000137329102</v>
@@ -3396,11 +3408,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>48.33962249755859</v>
+        <v>48.33961868286133</v>
       </c>
       <c r="C120" t="n">
         <v>63.58000183105469</v>
@@ -3425,11 +3437,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>47.32421493530273</v>
+        <v>47.3242301940918</v>
       </c>
       <c r="C121" t="n">
         <v>61.97000122070312</v>
@@ -3454,11 +3466,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>43.13171768188477</v>
+        <v>43.13171005249023</v>
       </c>
       <c r="C122" t="n">
         <v>56.47999954223633</v>
@@ -3483,11 +3495,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>38.33589935302734</v>
+        <v>38.33589172363281</v>
       </c>
       <c r="C123" t="n">
         <v>50.20000076293945</v>
@@ -3512,11 +3524,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>41.53361511230469</v>
+        <v>41.53362274169922</v>
       </c>
       <c r="C124" t="n">
         <v>54.04999923706055</v>
@@ -3541,11 +3553,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>42.89374542236328</v>
+        <v>42.89374923706055</v>
       </c>
       <c r="C125" t="n">
         <v>55.81999969482422</v>
@@ -3570,11 +3582,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>44.47671508789062</v>
+        <v>44.47672271728516</v>
       </c>
       <c r="C126" t="n">
         <v>57.88000106811523</v>
@@ -3597,11 +3609,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.87203979492188</v>
+        <v>40.87203216552734</v>
       </c>
       <c r="C127" t="n">
         <v>52.88999938964844</v>
@@ -3624,7 +3636,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>46.23508453369141</v>
+        <v>46.23507690429688</v>
       </c>
       <c r="C129" t="n">
         <v>59.83000183105469</v>
@@ -3680,7 +3692,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3709,11 +3721,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>47.94022750854492</v>
+        <v>47.94023513793945</v>
       </c>
       <c r="C131" t="n">
         <v>61.70000076293945</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>49.20672607421875</v>
+        <v>49.20672225952148</v>
       </c>
       <c r="C132" t="n">
         <v>63.33000183105469</v>
@@ -3767,11 +3779,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.99928665161133</v>
+        <v>50.9992790222168</v>
       </c>
       <c r="C133" t="n">
         <v>65.30999755859375</v>
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>50.17934417724609</v>
+        <v>50.17935562133789</v>
       </c>
       <c r="C134" t="n">
         <v>64.26000213623047</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>49.91386032104492</v>
+        <v>49.91385650634766</v>
       </c>
       <c r="C135" t="n">
         <v>63.91999816894531</v>
@@ -3852,11 +3864,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>48.99890899658203</v>
+        <v>48.99891662597656</v>
       </c>
       <c r="C136" t="n">
         <v>62.43000030517578</v>
@@ -3879,11 +3891,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>47.8059196472168</v>
+        <v>47.80592346191406</v>
       </c>
       <c r="C137" t="n">
         <v>60.90999984741211</v>
@@ -3906,11 +3918,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>49.94074630737305</v>
+        <v>49.94075012207031</v>
       </c>
       <c r="C138" t="n">
         <v>63.63000106811523</v>
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>49.3154411315918</v>
+        <v>49.31544876098633</v>
       </c>
       <c r="C139" t="n">
         <v>62.52000045776367</v>
@@ -3964,11 +3976,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.62659454345703</v>
+        <v>51.62660598754883</v>
       </c>
       <c r="C140" t="n">
         <v>65.44999694824219</v>
@@ -3993,7 +4005,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>48.68057250976562</v>
+        <v>48.68056106567383</v>
       </c>
       <c r="C142" t="n">
         <v>61.38999938964844</v>
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.23393249511719</v>
+        <v>51.23394012451172</v>
       </c>
       <c r="C143" t="n">
         <v>64.61000061035156</v>
@@ -4080,7 +4092,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4107,11 +4119,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>47.49848937988281</v>
+        <v>47.49848175048828</v>
       </c>
       <c r="C145" t="n">
         <v>59.58000183105469</v>
@@ -4134,11 +4146,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>50.95842361450195</v>
+        <v>50.95843124389648</v>
       </c>
       <c r="C146" t="n">
         <v>63.91999816894531</v>
@@ -4161,11 +4173,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>45.71271133422852</v>
+        <v>45.71270370483398</v>
       </c>
       <c r="C147" t="n">
         <v>57.34000015258789</v>
@@ -4188,11 +4200,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>43.63441467285156</v>
+        <v>43.63443374633789</v>
       </c>
       <c r="C148" t="n">
         <v>54.41999816894531</v>
@@ -4215,11 +4227,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>44.90129089355469</v>
+        <v>44.90127944946289</v>
       </c>
       <c r="C149" t="n">
         <v>56</v>
@@ -4242,11 +4254,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>42.32748413085938</v>
+        <v>42.32748031616211</v>
       </c>
       <c r="C150" t="n">
         <v>52.79000091552734</v>
@@ -4269,11 +4281,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.76269912719727</v>
+        <v>42.76271057128906</v>
       </c>
       <c r="C151" t="n">
         <v>53.02000045776367</v>
@@ -4296,11 +4308,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>44.52903366088867</v>
+        <v>44.52902221679688</v>
       </c>
       <c r="C152" t="n">
         <v>55.20999908447266</v>
@@ -4323,7 +4335,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4350,11 +4362,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>43.20261764526367</v>
+        <v>43.20262145996094</v>
       </c>
       <c r="C154" t="n">
         <v>53.2400016784668</v>
@@ -4377,11 +4389,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>33.50556564331055</v>
+        <v>33.50557327270508</v>
       </c>
       <c r="C155" t="n">
         <v>41.29000091552734</v>
@@ -4404,11 +4416,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>35.09605026245117</v>
+        <v>35.09604644775391</v>
       </c>
       <c r="C156" t="n">
         <v>43.25</v>
@@ -4431,11 +4443,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>32.25516891479492</v>
+        <v>32.25517654418945</v>
       </c>
       <c r="C157" t="n">
         <v>39.40999984741211</v>
@@ -4458,7 +4470,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.35710525512695</v>
+        <v>35.35711288452148</v>
       </c>
       <c r="C159" t="n">
         <v>43.20000076293945</v>
@@ -4512,11 +4524,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.5019645690918</v>
+        <v>35.50196075439453</v>
       </c>
       <c r="C160" t="n">
         <v>43.06000137329102</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.22034454345703</v>
+        <v>39.2203369140625</v>
       </c>
       <c r="C161" t="n">
         <v>47.56999969482422</v>
@@ -4566,11 +4578,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>42.10600280761719</v>
+        <v>42.10600662231445</v>
       </c>
       <c r="C162" t="n">
         <v>51.06999969482422</v>
@@ -4593,11 +4605,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>44.19513320922852</v>
+        <v>44.19513702392578</v>
       </c>
       <c r="C163" t="n">
         <v>53.27999877929688</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>46.44305419921875</v>
+        <v>46.44305801391602</v>
       </c>
       <c r="C164" t="n">
         <v>55.9900016784668</v>
@@ -4647,11 +4659,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>43.16657638549805</v>
+        <v>43.16658020019531</v>
       </c>
       <c r="C165" t="n">
         <v>52.04000091552734</v>
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>46.4620246887207</v>
+        <v>46.46203231811523</v>
       </c>
       <c r="C166" t="n">
         <v>55.70000076293945</v>
@@ -4701,11 +4713,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>44.17645645141602</v>
+        <v>44.17646026611328</v>
       </c>
       <c r="C167" t="n">
         <v>52.95999908447266</v>
@@ -4728,11 +4740,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>43.92621612548828</v>
+        <v>43.92621231079102</v>
       </c>
       <c r="C168" t="n">
         <v>52.65999984741211</v>
@@ -4757,7 +4769,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4786,11 +4798,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>42.18855285644531</v>
+        <v>42.18855667114258</v>
       </c>
       <c r="C170" t="n">
         <v>50.2599983215332</v>
@@ -4815,11 +4827,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>35.38936233520508</v>
+        <v>35.38936996459961</v>
       </c>
       <c r="C171" t="n">
         <v>42.15999984741211</v>
@@ -4844,11 +4856,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>20.61255836486816</v>
+        <v>20.61255264282227</v>
       </c>
       <c r="C172" t="n">
         <v>24.25</v>
@@ -4873,11 +4885,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>21.61555480957031</v>
+        <v>21.61555862426758</v>
       </c>
       <c r="C173" t="n">
         <v>25.43000030517578</v>
@@ -4902,11 +4914,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>25.55106735229492</v>
+        <v>25.55106925964355</v>
       </c>
       <c r="C174" t="n">
         <v>30.05999946594238</v>
@@ -4931,7 +4943,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4960,11 +4972,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>27.59846115112305</v>
+        <v>27.59846496582031</v>
       </c>
       <c r="C176" t="n">
         <v>32.13999938964844</v>
@@ -4989,11 +5001,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>25.02238082885742</v>
+        <v>25.02237510681152</v>
       </c>
       <c r="C177" t="n">
         <v>29.13999938964844</v>
@@ -5016,11 +5028,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>23.90428924560547</v>
+        <v>23.90429306030273</v>
       </c>
       <c r="C178" t="n">
         <v>27.53000068664551</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>27.34275436401367</v>
+        <v>27.3427562713623</v>
       </c>
       <c r="C179" t="n">
         <v>31.48999977111816</v>
@@ -5070,11 +5082,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>33.37743759155273</v>
+        <v>33.37743377685547</v>
       </c>
       <c r="C180" t="n">
         <v>38.43999862670898</v>
@@ -5097,7 +5109,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>32.77324295043945</v>
+        <v>32.77323913574219</v>
       </c>
       <c r="C182" t="n">
         <v>37.43999862670898</v>
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5178,11 +5190,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>40.71908569335938</v>
+        <v>40.71908187866211</v>
       </c>
       <c r="C184" t="n">
         <v>46.20999908447266</v>
@@ -5205,11 +5217,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>42.69292449951172</v>
+        <v>42.69291687011719</v>
       </c>
       <c r="C185" t="n">
         <v>48.45000076293945</v>
@@ -5232,11 +5244,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>46.561279296875</v>
+        <v>46.56127166748047</v>
       </c>
       <c r="C186" t="n">
         <v>52.84000015258789</v>
@@ -5259,11 +5271,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>42.20352935791016</v>
+        <v>42.20352554321289</v>
       </c>
       <c r="C187" t="n">
         <v>47.59999847412109</v>
@@ -5286,11 +5298,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>41.98187637329102</v>
+        <v>41.98188018798828</v>
       </c>
       <c r="C188" t="n">
         <v>47.34999847412109</v>
@@ -5313,11 +5325,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>48.37446975708008</v>
+        <v>48.37446594238281</v>
       </c>
       <c r="C189" t="n">
         <v>54.56000137329102</v>
@@ -5342,11 +5354,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>48.95487213134766</v>
+        <v>48.95486450195312</v>
       </c>
       <c r="C190" t="n">
         <v>54.88999938964844</v>
@@ -5371,11 +5383,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>52.70073318481445</v>
+        <v>52.70073699951172</v>
       </c>
       <c r="C191" t="n">
         <v>59.09000015258789</v>
@@ -5400,7 +5412,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5429,11 +5441,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>51.01049423217773</v>
+        <v>51.0104866027832</v>
       </c>
       <c r="C193" t="n">
         <v>56.86000061035156</v>
@@ -5458,11 +5470,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>51.80892562866211</v>
+        <v>51.80892181396484</v>
       </c>
       <c r="C194" t="n">
         <v>57.75</v>
@@ -5487,11 +5499,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>54.93989562988281</v>
+        <v>54.93989944458008</v>
       </c>
       <c r="C195" t="n">
         <v>61.2400016784668</v>
@@ -5516,11 +5528,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>56.6219596862793</v>
+        <v>56.62195205688477</v>
       </c>
       <c r="C196" t="n">
         <v>62.77000045776367</v>
@@ -5545,11 +5557,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>52.77919769287109</v>
+        <v>52.77920150756836</v>
       </c>
       <c r="C197" t="n">
         <v>58.5099983215332</v>
@@ -5574,11 +5586,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>52.93254852294922</v>
+        <v>52.93255615234375</v>
       </c>
       <c r="C198" t="n">
         <v>58.68000030517578</v>
@@ -5603,11 +5615,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>46.40752029418945</v>
+        <v>46.40751266479492</v>
       </c>
       <c r="C199" t="n">
         <v>51.13000106811523</v>
@@ -5632,11 +5644,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>46.9884033203125</v>
+        <v>46.98840713500977</v>
       </c>
       <c r="C200" t="n">
         <v>51.77000045776367</v>
@@ -5661,7 +5673,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5690,11 +5702,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>43.35058975219727</v>
+        <v>43.3505859375</v>
       </c>
       <c r="C202" t="n">
         <v>47.47999954223633</v>
@@ -5719,11 +5731,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>52.0426139831543</v>
+        <v>52.04261779785156</v>
       </c>
       <c r="C203" t="n">
         <v>57</v>
@@ -5748,11 +5760,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>57.62121963500977</v>
+        <v>57.62122344970703</v>
       </c>
       <c r="C204" t="n">
         <v>63.11000061035156</v>
@@ -5777,11 +5789,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>58.03208923339844</v>
+        <v>58.03208541870117</v>
       </c>
       <c r="C205" t="n">
         <v>63.2400016784668</v>
@@ -5806,11 +5818,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>58.01372146606445</v>
+        <v>58.01373291015625</v>
       </c>
       <c r="C206" t="n">
         <v>63.22000122070312</v>
@@ -5835,11 +5847,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>56.07749176025391</v>
+        <v>56.07749557495117</v>
       </c>
       <c r="C207" t="n">
         <v>61.11000061035156</v>
@@ -5864,11 +5876,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>46.5231819152832</v>
+        <v>46.52318572998047</v>
       </c>
       <c r="C208" t="n">
         <v>50.36000061035156</v>
@@ -5893,11 +5905,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>48.99900054931641</v>
+        <v>48.99900436401367</v>
       </c>
       <c r="C209" t="n">
         <v>53.04000091552734</v>
@@ -5922,11 +5934,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>48.80500411987305</v>
+        <v>48.80500030517578</v>
       </c>
       <c r="C210" t="n">
         <v>52.83000183105469</v>
@@ -5951,11 +5963,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>53.50107574462891</v>
+        <v>53.50107955932617</v>
       </c>
       <c r="C211" t="n">
         <v>57.54000091552734</v>
@@ -5980,11 +5992,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>56.04874420166016</v>
+        <v>56.04875183105469</v>
       </c>
       <c r="C212" t="n">
         <v>60.27999877929688</v>
@@ -6009,11 +6021,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>54.41229248046875</v>
+        <v>54.41228485107422</v>
       </c>
       <c r="C213" t="n">
         <v>58.52000045776367</v>
@@ -6038,7 +6050,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6067,11 +6079,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>57.34684371948242</v>
+        <v>57.34683990478516</v>
       </c>
       <c r="C215" t="n">
         <v>61.31000137329102</v>
@@ -6096,11 +6108,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>61.55594635009766</v>
+        <v>61.55595016479492</v>
       </c>
       <c r="C216" t="n">
         <v>65.80999755859375</v>
@@ -6125,11 +6137,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>63.71315765380859</v>
+        <v>63.71315383911133</v>
       </c>
       <c r="C217" t="n">
         <v>67.75</v>
@@ -6154,11 +6166,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>65.36827850341797</v>
+        <v>65.36829376220703</v>
       </c>
       <c r="C218" t="n">
         <v>69.51000213623047</v>
@@ -6183,11 +6195,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>68.54688262939453</v>
+        <v>68.54689025878906</v>
       </c>
       <c r="C219" t="n">
         <v>72.88999938964844</v>
@@ -6212,7 +6224,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6241,7 +6253,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6270,7 +6282,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6299,11 +6311,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>70.52988433837891</v>
+        <v>70.52987670898438</v>
       </c>
       <c r="C223" t="n">
         <v>74.23999786376953</v>
@@ -6328,11 +6340,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>75.27050018310547</v>
+        <v>75.27052307128906</v>
       </c>
       <c r="C224" t="n">
         <v>79.23000335693359</v>
@@ -6357,7 +6369,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6384,11 +6396,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>69.95309448242188</v>
+        <v>69.95310211181641</v>
       </c>
       <c r="C226" t="n">
         <v>73.23000335693359</v>
@@ -6411,11 +6423,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>72.48450469970703</v>
+        <v>72.48451232910156</v>
       </c>
       <c r="C227" t="n">
         <v>75.87999725341797</v>
@@ -6438,11 +6450,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>73.43975830078125</v>
+        <v>73.43977355957031</v>
       </c>
       <c r="C228" t="n">
         <v>76.87999725341797</v>
@@ -6465,11 +6477,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>69.92618560791016</v>
+        <v>69.92617034912109</v>
       </c>
       <c r="C229" t="n">
         <v>72.80000305175781</v>
@@ -6492,7 +6504,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6519,7 +6531,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6546,11 +6558,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>83.91175079345703</v>
+        <v>83.9117431640625</v>
       </c>
       <c r="C232" t="n">
         <v>86.94000244140625</v>
@@ -6573,11 +6585,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>78.68052673339844</v>
+        <v>78.68053436279297</v>
       </c>
       <c r="C233" t="n">
         <v>81.51999664306641</v>
@@ -6600,7 +6612,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6654,11 +6666,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>75.32107543945312</v>
+        <v>75.32106018066406</v>
       </c>
       <c r="C236" t="n">
         <v>77.62999725341797</v>
@@ -6681,7 +6693,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6710,7 +6722,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6739,11 +6751,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>77.06169891357422</v>
+        <v>77.06169128417969</v>
       </c>
       <c r="C239" t="n">
         <v>78.95999908447266</v>
@@ -6768,11 +6780,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>74.32902526855469</v>
+        <v>74.32901763916016</v>
       </c>
       <c r="C240" t="n">
         <v>76.16000366210938</v>
@@ -6797,7 +6809,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6826,7 +6838,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6855,7 +6867,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6884,7 +6896,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6913,7 +6925,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6942,7 +6954,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6971,7 +6983,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7000,7 +7012,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7029,7 +7041,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7058,32 +7070,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>75.58000183105469</v>
+        <v>74.81999969482422</v>
       </c>
       <c r="C250" t="n">
-        <v>75.58000183105469</v>
+        <v>74.81999969482422</v>
       </c>
       <c r="D250" t="n">
-        <v>74706700</v>
+        <v>77874800</v>
       </c>
       <c r="E250" t="n">
         <v>5.480000000000003</v>
       </c>
       <c r="F250" t="n">
-        <v>13.79197113705377</v>
+        <v>13.65328461584383</v>
       </c>
       <c r="G250" t="n">
         <v>522893169</v>
       </c>
       <c r="H250" t="n">
-        <v>39520266670.46599</v>
+        <v>39122866745.00567</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1428718224467759</v>
+        <v>0.1489306126315068</v>
       </c>
     </row>
   </sheetData>
@@ -7115,75 +7127,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7219,13 +7231,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7261,13 +7273,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7471,13 +7483,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7504,7 +7516,7 @@
       <c r="I9" t="n">
         <v>11.47712033188235</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K9" t="n">
@@ -7517,13 +7529,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7550,7 +7562,7 @@
       <c r="I10" t="n">
         <v>8.962394529504214</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K10" t="n">
@@ -7563,13 +7575,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7596,7 +7608,7 @@
       <c r="I11" t="n">
         <v>13.92383138726217</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K11" t="n">
@@ -7609,13 +7621,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7642,7 +7654,7 @@
       <c r="I12" t="n">
         <v>29.38659109758385</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K12" t="n">
@@ -7655,13 +7667,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7688,7 +7700,7 @@
       <c r="I13" t="n">
         <v>8.91631524485911</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K13" t="n">
@@ -7701,13 +7713,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7734,7 +7746,7 @@
       <c r="I14" t="n">
         <v>10.97491408812762</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K14" t="n">
@@ -7747,13 +7759,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7780,7 +7792,7 @@
       <c r="I15" t="n">
         <v>11.3006344952425</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K15" t="n">
@@ -7793,13 +7805,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7826,7 +7838,7 @@
       <c r="I16" t="n">
         <v>14.59381785307631</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K16" t="n">
@@ -7839,13 +7851,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7872,7 +7884,7 @@
       <c r="I17" t="n">
         <v>1.486739387996394</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K17" t="n">
@@ -7885,13 +7897,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7918,7 +7930,7 @@
       <c r="I18" t="n">
         <v>1.266720595513531</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K18" t="n">
@@ -7931,13 +7943,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7964,7 +7976,7 @@
       <c r="I19" t="n">
         <v>1.779242491822264</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="K19" t="n">
@@ -7977,13 +7989,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8010,7 +8022,7 @@
       <c r="I20" t="n">
         <v>2.109259261132616</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K20" t="n">
@@ -8023,13 +8035,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8056,7 +8068,7 @@
       <c r="I21" t="n">
         <v>6.130000000000003</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K21" t="n">
@@ -8069,13 +8081,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8102,7 +8114,7 @@
       <c r="I22" t="n">
         <v>5.730000000000003</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K22" t="n">
@@ -8115,13 +8127,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8148,7 +8160,7 @@
       <c r="I23" t="n">
         <v>5.990000000000004</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K23" t="n">
@@ -8161,13 +8173,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="I24" t="n">
         <v>6.050000000000003</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K24" t="n">
@@ -8207,13 +8219,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8240,7 +8252,7 @@
       <c r="I25" t="n">
         <v>5.200000000000003</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K25" t="n">
@@ -8253,13 +8265,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8286,7 +8298,7 @@
       <c r="I26" t="n">
         <v>5.890000000000003</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K26" t="n">
@@ -8299,13 +8311,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8332,7 +8344,7 @@
       <c r="I27" t="n">
         <v>5.110000000000003</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K27" t="n">
@@ -8345,13 +8357,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8378,7 +8390,7 @@
       <c r="I28" t="n">
         <v>3.410000000000002</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K28" t="n">
@@ -8391,13 +8403,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8424,7 +8436,7 @@
       <c r="I29" t="n">
         <v>1.650000000000003</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K29" t="n">
@@ -8437,13 +8449,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8470,7 +8482,7 @@
       <c r="I30" t="n">
         <v>-0.2899999999999968</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K30" t="n">
@@ -8483,13 +8495,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8516,7 +8528,7 @@
       <c r="I31" t="n">
         <v>0.07000000000000317</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K31" t="n">
@@ -8529,13 +8541,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8562,7 +8574,7 @@
       <c r="I32" t="n">
         <v>0.6700000000000029</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K32" t="n">
@@ -8575,13 +8587,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8608,7 +8620,7 @@
       <c r="I33" t="n">
         <v>-0.7799999999999967</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K33" t="n">
@@ -8621,13 +8633,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8654,7 +8666,7 @@
       <c r="I34" t="n">
         <v>0.5600000000000033</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K34" t="n">
@@ -8667,13 +8679,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8700,7 +8712,7 @@
       <c r="I35" t="n">
         <v>0.07000000000000339</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K35" t="n">
@@ -8713,13 +8725,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8746,7 +8758,7 @@
       <c r="I36" t="n">
         <v>-2.259999999999997</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K36" t="n">
@@ -8759,13 +8771,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="I37" t="n">
         <v>-6.539999999999997</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K37" t="n">
@@ -8805,13 +8817,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="I38" t="n">
         <v>-6.709999999999997</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K38" t="n">
@@ -8851,13 +8863,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8884,7 +8896,7 @@
       <c r="I39" t="n">
         <v>-6.879999999999997</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K39" t="n">
@@ -8897,13 +8909,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8930,7 +8942,7 @@
       <c r="I40" t="n">
         <v>-6.379999999999997</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K40" t="n">
@@ -8943,13 +8955,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8976,7 +8988,7 @@
       <c r="I41" t="n">
         <v>-0.009999999999997566</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K41" t="n">
@@ -8989,13 +9001,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9022,7 +9034,7 @@
       <c r="I42" t="n">
         <v>-0.2699999999999976</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="K42" t="n">
@@ -9035,13 +9047,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9068,7 +9080,7 @@
       <c r="I43" t="n">
         <v>-0.0499999999999976</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="K43" t="n">
@@ -9081,13 +9093,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9114,7 +9126,7 @@
       <c r="I44" t="n">
         <v>2.080000000000002</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K44" t="n">
@@ -9127,13 +9139,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9160,7 +9172,7 @@
       <c r="I45" t="n">
         <v>3.740000000000003</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K45" t="n">
@@ -9173,13 +9185,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9206,7 +9218,7 @@
       <c r="I46" t="n">
         <v>4.970000000000002</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K46" t="n">
@@ -9219,13 +9231,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9252,7 +9264,7 @@
       <c r="I47" t="n">
         <v>-5.419999999999998</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K47" t="n">
@@ -9265,13 +9277,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9298,7 +9310,7 @@
       <c r="I48" t="n">
         <v>-5.819999999999998</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K48" t="n">
@@ -9311,13 +9323,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9344,7 +9356,7 @@
       <c r="I49" t="n">
         <v>-6.879999999999998</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="K49" t="n">
@@ -9357,13 +9369,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9390,7 +9402,7 @@
       <c r="I50" t="n">
         <v>-4.449999999999998</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="K50" t="n">
@@ -9403,13 +9415,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9436,7 +9448,7 @@
       <c r="I51" t="n">
         <v>4.810000000000003</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K51" t="n">
@@ -9449,13 +9461,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9482,7 +9494,7 @@
       <c r="I52" t="n">
         <v>6.410000000000003</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K52" t="n">
@@ -9495,13 +9507,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9528,7 +9540,7 @@
       <c r="I53" t="n">
         <v>10.82</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K53" t="n">
@@ -9541,13 +9553,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9574,7 +9586,7 @@
       <c r="I54" t="n">
         <v>11.56</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K54" t="n">
@@ -9587,13 +9599,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9620,7 +9632,7 @@
       <c r="I55" t="n">
         <v>15.23</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="K55" t="n">
@@ -9633,13 +9645,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="I56" t="n">
         <v>16.81</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K56" t="n">
@@ -9679,13 +9691,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9712,7 +9724,7 @@
       <c r="I57" t="n">
         <v>13.01</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="K57" t="n">
@@ -9725,13 +9737,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9758,7 +9770,7 @@
       <c r="I58" t="n">
         <v>7.890000000000002</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K58" t="n">
@@ -9771,13 +9783,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="I59" t="n">
         <v>6.140000000000002</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K59" t="n">
@@ -9817,13 +9829,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9850,7 +9862,7 @@
       <c r="I60" t="n">
         <v>5.450000000000003</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K60" t="n">
@@ -9863,13 +9875,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9896,7 +9908,7 @@
       <c r="I61" t="n">
         <v>4.980000000000004</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="K61" t="n">
@@ -9909,13 +9921,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="I62" t="n">
         <v>6.690000000000003</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K62" t="n">
@@ -9955,13 +9967,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9988,7 +10000,7 @@
       <c r="I63" t="n">
         <v>-1.299999999999996</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K63" t="n">
@@ -10001,13 +10013,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10034,7 +10046,7 @@
       <c r="I64" t="n">
         <v>-3.399999999999996</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K64" t="n">
@@ -10047,13 +10059,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10080,7 +10092,7 @@
       <c r="I65" t="n">
         <v>-2.169999999999998</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K65" t="n">
@@ -10093,13 +10105,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10126,7 +10138,7 @@
       <c r="I66" t="n">
         <v>-2.749999999999997</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K66" t="n">
@@ -10139,13 +10151,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10172,7 +10184,7 @@
       <c r="I67" t="n">
         <v>5.190000000000002</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K67" t="n">
@@ -10185,13 +10197,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10218,7 +10230,7 @@
       <c r="I68" t="n">
         <v>5.410000000000003</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K68" t="n">
@@ -10231,13 +10243,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10264,7 +10276,7 @@
       <c r="I69" t="n">
         <v>5.430000000000003</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K69" t="n">
@@ -10277,13 +10289,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10310,7 +10322,7 @@
       <c r="I70" t="n">
         <v>5.680000000000002</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K70" t="n">
@@ -10323,13 +10335,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10356,7 +10368,7 @@
       <c r="I71" t="n">
         <v>5.480000000000003</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K71" t="n">
@@ -10393,52 +10405,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="C2" t="n">
@@ -10467,10 +10479,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10499,10 +10511,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10531,10 +10543,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10563,10 +10575,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10595,10 +10607,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10627,10 +10639,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C8" t="n">
@@ -10659,10 +10671,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10691,10 +10703,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10723,10 +10735,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10755,10 +10767,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -10787,10 +10799,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10819,10 +10831,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -10851,10 +10863,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C15" t="n">
@@ -10883,10 +10895,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C16" t="n">
@@ -10915,10 +10927,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41389</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -10947,10 +10959,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="C18" t="n">
@@ -10979,10 +10991,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C19" t="n">
@@ -11011,10 +11023,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C20" t="n">
@@ -11043,10 +11055,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41758</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C21" t="n">
@@ -11075,10 +11087,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41850</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C22" t="n">
@@ -11107,10 +11119,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41941</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C23" t="n">
@@ -11139,10 +11151,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42047</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C24" t="n">
@@ -11171,10 +11183,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42123</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C25" t="n">
@@ -11203,10 +11215,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42214</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11235,10 +11247,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42306</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C27" t="n">
@@ -11267,10 +11279,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42411</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C28" t="n">
@@ -11299,10 +11311,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42487</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C29" t="n">
@@ -11331,10 +11343,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C30" t="n">
@@ -11363,10 +11375,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42676</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11395,10 +11407,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42779</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11427,10 +11439,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11459,10 +11471,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11491,10 +11503,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C35" t="n">
@@ -11523,10 +11535,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43138</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C36" t="n">
@@ -11555,10 +11567,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C37" t="n">
@@ -11587,10 +11599,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C38" t="n">
@@ -11619,10 +11631,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C39" t="n">
@@ -11651,10 +11663,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43502</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="C40" t="n">
@@ -11683,10 +11695,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43587</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="C41" t="n">
@@ -11715,10 +11727,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C42" t="n">
@@ -11747,10 +11759,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C43" t="n">
@@ -11779,10 +11791,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43871</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C44" t="n">
@@ -11811,10 +11823,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -11843,10 +11855,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -11875,10 +11887,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44137</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C47" t="n">
@@ -11907,10 +11919,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44236</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="C48" t="n">
@@ -11939,10 +11951,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C49" t="n">
@@ -11971,10 +11983,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C50" t="n">
@@ -12003,10 +12015,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C51" t="n">
@@ -12035,10 +12047,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44600</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C52" t="n">
@@ -12067,10 +12079,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44677</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C53" t="n">
@@ -12099,10 +12111,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44776</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="C54" t="n">
@@ -12131,10 +12143,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44861</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12163,10 +12175,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="C56" t="n">
@@ -12195,10 +12207,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C57" t="n">
@@ -12227,10 +12239,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12259,10 +12271,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12291,10 +12303,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45330</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="C60" t="n">
@@ -12323,10 +12335,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12355,10 +12367,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12387,10 +12399,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C63" t="n">
@@ -12419,10 +12431,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C64" t="n">
@@ -12451,10 +12463,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12483,10 +12495,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C66" t="n">
@@ -12515,10 +12527,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C67" t="n">
@@ -12547,10 +12559,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C68" t="n">
@@ -12579,10 +12591,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12611,10 +12623,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C70" t="n">
@@ -12661,12 +12673,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AIG.xlsx
+++ b/salidas/empresas/AIG.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>774.8095092773438</v>
+        <v>774.809326171875</v>
       </c>
       <c r="C2" t="n">
         <v>1309.199951171875</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>785.4620971679688</v>
+        <v>785.4617919921875</v>
       </c>
       <c r="C3" t="n">
         <v>1327.199951171875</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>784.0383911132812</v>
+        <v>784.0384521484375</v>
       </c>
       <c r="C4" t="n">
         <v>1321.800048828125</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>774.0734252929688</v>
+        <v>774.0733032226562</v>
       </c>
       <c r="C5" t="n">
         <v>1305</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>723.0718994140625</v>
+        <v>723.0719604492188</v>
       </c>
       <c r="C6" t="n">
         <v>1216</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>702.2599487304688</v>
+        <v>702.2596435546875</v>
       </c>
       <c r="C7" t="n">
         <v>1181</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>721.5256958007812</v>
+        <v>721.5257568359375</v>
       </c>
       <c r="C8" t="n">
         <v>1213.400024414062</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>760.961669921875</v>
+        <v>760.9620971679688</v>
       </c>
       <c r="C9" t="n">
         <v>1276.400024414062</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>790.0552368164062</v>
+        <v>790.055419921875</v>
       </c>
       <c r="C10" t="n">
         <v>1325.199951171875</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>800.9056396484375</v>
+        <v>800.9055786132812</v>
       </c>
       <c r="C11" t="n">
         <v>1343.400024414062</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>840.4503173828125</v>
+        <v>840.4505004882812</v>
       </c>
       <c r="C12" t="n">
         <v>1406.400024414062</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>856.4657592773438</v>
+        <v>856.4660034179688</v>
       </c>
       <c r="C13" t="n">
         <v>1433.199951171875</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>818.1004028320312</v>
+        <v>818.1006469726562</v>
       </c>
       <c r="C14" t="n">
         <v>1369</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>804.0718994140625</v>
+        <v>804.072021484375</v>
       </c>
       <c r="C15" t="n">
         <v>1342.199951171875</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>805.3901977539062</v>
+        <v>805.3900756835938</v>
       </c>
       <c r="C16" t="n">
         <v>1344.400024414062</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>837.6201171875</v>
+        <v>837.619873046875</v>
       </c>
       <c r="C17" t="n">
         <v>1398.199951171875</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>868.7284545898438</v>
+        <v>868.7286987304688</v>
       </c>
       <c r="C18" t="n">
         <v>1446.800048828125</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>840.9876098632812</v>
+        <v>840.9879760742188</v>
       </c>
       <c r="C19" t="n">
         <v>1400.599975585938</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>770.7351684570312</v>
+        <v>770.735595703125</v>
       </c>
       <c r="C20" t="n">
         <v>1283.599975585938</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>792.5914306640625</v>
+        <v>792.5919189453125</v>
       </c>
       <c r="C21" t="n">
         <v>1320</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>760.2904052734375</v>
+        <v>760.29052734375</v>
       </c>
       <c r="C23" t="n">
         <v>1262.400024414062</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>704.7655639648438</v>
+        <v>704.7656860351562</v>
       </c>
       <c r="C25" t="n">
         <v>1166</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>664.5106201171875</v>
+        <v>664.5108032226562</v>
       </c>
       <c r="C26" t="n">
         <v>1099.400024414062</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>566.4718627929688</v>
+        <v>566.4721069335938</v>
       </c>
       <c r="C27" t="n">
         <v>937.2000122070312</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>525.1239624023438</v>
+        <v>525.1238403320312</v>
       </c>
       <c r="C28" t="n">
         <v>865</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>560.9415893554688</v>
+        <v>560.9414672851562</v>
       </c>
       <c r="C29" t="n">
         <v>924</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>437.0973205566406</v>
+        <v>437.0972290039062</v>
       </c>
       <c r="C30" t="n">
         <v>720</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>323.0607604980469</v>
+        <v>323.0606994628906</v>
       </c>
       <c r="C31" t="n">
         <v>529.2000122070312</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>318.0549621582031</v>
+        <v>318.0549011230469</v>
       </c>
       <c r="C32" t="n">
         <v>521</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>23.55594253540039</v>
+        <v>23.55594825744629</v>
       </c>
       <c r="C35" t="n">
         <v>38.20000076293945</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>24.78923797607422</v>
+        <v>24.78923606872559</v>
       </c>
       <c r="C36" t="n">
         <v>40.20000076293945</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>19.36274147033691</v>
+        <v>19.36273956298828</v>
       </c>
       <c r="C37" t="n">
         <v>31.39999961853027</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.78617858886719</v>
+        <v>15.78618240356445</v>
       </c>
       <c r="C38" t="n">
         <v>25.60000038146973</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.179841041564941</v>
+        <v>5.179842472076416</v>
       </c>
       <c r="C39" t="n">
         <v>8.399999618530273</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.3329553604126</v>
+        <v>12.33295631408691</v>
       </c>
       <c r="C40" t="n">
         <v>20</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>17.01948165893555</v>
+        <v>17.01948356628418</v>
       </c>
       <c r="C41" t="n">
         <v>27.60000038146973</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.84269523620605</v>
+        <v>20.84269142150879</v>
       </c>
       <c r="C42" t="n">
         <v>33.79999923706055</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>8.102753639221191</v>
+        <v>8.102750778198242</v>
       </c>
       <c r="C44" t="n">
         <v>13.14000034332275</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>27.95264434814453</v>
+        <v>27.95264053344727</v>
       </c>
       <c r="C45" t="n">
         <v>45.33000183105469</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.51279449462891</v>
+        <v>17.5128002166748</v>
       </c>
       <c r="C48" t="n">
         <v>28.39999961853027</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>18.48710060119629</v>
+        <v>18.48709869384766</v>
       </c>
       <c r="C49" t="n">
         <v>29.97999954223633</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.94138145446777</v>
+        <v>14.94137763977051</v>
       </c>
       <c r="C50" t="n">
         <v>24.22999954223633</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.27436351776123</v>
+        <v>15.27437114715576</v>
       </c>
       <c r="C51" t="n">
         <v>24.77000045776367</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.0523509979248</v>
+        <v>21.05236053466797</v>
       </c>
       <c r="C52" t="n">
         <v>34.13999938964844</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.98760032653809</v>
+        <v>23.98760223388672</v>
       </c>
       <c r="C53" t="n">
         <v>38.90000152587891</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>21.8169994354248</v>
+        <v>21.81700325012207</v>
       </c>
       <c r="C54" t="n">
         <v>35.38000106811523</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.23735046386719</v>
+        <v>21.23734855651855</v>
       </c>
       <c r="C55" t="n">
         <v>34.43999862670898</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.72244071960449</v>
+        <v>23.72243881225586</v>
       </c>
       <c r="C56" t="n">
         <v>38.47000122070312</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.11092758178711</v>
+        <v>24.11092185974121</v>
       </c>
       <c r="C58" t="n">
         <v>39.09999847412109</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>25.9053783416748</v>
+        <v>25.90537261962891</v>
       </c>
       <c r="C59" t="n">
         <v>42.0099983215332</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>35.53125</v>
+        <v>35.53124237060547</v>
       </c>
       <c r="C61" t="n">
         <v>57.61999893188477</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>29.99683570861816</v>
+        <v>29.99684715270996</v>
       </c>
       <c r="C62" t="n">
         <v>40.34999847412109</v>
@@ -1759,7 +1759,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.55100250244141</v>
+        <v>27.55099868774414</v>
       </c>
       <c r="C63" t="n">
         <v>37.06000137329102</v>
@@ -1788,7 +1788,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>26.1236457824707</v>
+        <v>26.12364768981934</v>
       </c>
       <c r="C64" t="n">
         <v>35.13999938964844</v>
@@ -1817,7 +1817,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>23.15740394592285</v>
+        <v>23.15741539001465</v>
       </c>
       <c r="C65" t="n">
         <v>31.14999961853027</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>21.18736267089844</v>
+        <v>21.18736457824707</v>
       </c>
       <c r="C66" t="n">
         <v>28.5</v>
@@ -1875,7 +1875,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.79696655273438</v>
+        <v>21.79696083068848</v>
       </c>
       <c r="C67" t="n">
         <v>29.31999969482422</v>
@@ -1904,7 +1904,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.33604049682617</v>
+        <v>21.3360424041748</v>
       </c>
       <c r="C68" t="n">
         <v>28.70000076293945</v>
@@ -1962,7 +1962,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>16.3179874420166</v>
+        <v>16.3179817199707</v>
       </c>
       <c r="C70" t="n">
         <v>21.95000076293945</v>
@@ -1991,7 +1991,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>18.35495185852051</v>
+        <v>18.35493850708008</v>
       </c>
       <c r="C71" t="n">
         <v>24.69000053405762</v>
@@ -2020,7 +2020,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.32903099060059</v>
+        <v>17.32902908325195</v>
       </c>
       <c r="C72" t="n">
         <v>23.30999946594238</v>
@@ -2049,7 +2049,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.24725151062012</v>
+        <v>17.24726104736328</v>
       </c>
       <c r="C73" t="n">
         <v>23.20000076293945</v>
@@ -2107,7 +2107,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.72261238098145</v>
+        <v>21.72260856628418</v>
       </c>
       <c r="C75" t="n">
         <v>29.21999931335449</v>
@@ -2136,7 +2136,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.91951942443848</v>
+        <v>22.91951751708984</v>
       </c>
       <c r="C76" t="n">
         <v>30.82999992370605</v>
@@ -2165,7 +2165,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>25.29844856262207</v>
+        <v>25.2984504699707</v>
       </c>
       <c r="C77" t="n">
         <v>34.02999877929688</v>
@@ -2223,7 +2223,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>23.85622024536133</v>
+        <v>23.85622406005859</v>
       </c>
       <c r="C79" t="n">
         <v>32.09000015258789</v>
@@ -2252,7 +2252,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>23.24662399291992</v>
+        <v>23.24661827087402</v>
       </c>
       <c r="C80" t="n">
         <v>31.27000045776367</v>
@@ -2281,7 +2281,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.52147674560547</v>
+        <v>25.52148056030273</v>
       </c>
       <c r="C81" t="n">
         <v>34.33000183105469</v>
@@ -2310,7 +2310,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.37662124633789</v>
+        <v>24.37661552429199</v>
       </c>
       <c r="C82" t="n">
         <v>32.79000091552734</v>
@@ -2339,7 +2339,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.9675235748291</v>
+        <v>25.96751976013184</v>
       </c>
       <c r="C83" t="n">
         <v>34.93000030517578</v>
@@ -2368,7 +2368,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>24.6293773651123</v>
+        <v>24.62936973571777</v>
       </c>
       <c r="C84" t="n">
         <v>33.13000106811523</v>
@@ -2397,7 +2397,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>26.24258613586426</v>
+        <v>26.24258995056152</v>
       </c>
       <c r="C85" t="n">
         <v>35.29999923706055</v>
@@ -2426,7 +2426,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>28.12344169616699</v>
+        <v>28.12343406677246</v>
       </c>
       <c r="C86" t="n">
         <v>37.83000183105469</v>
@@ -2455,7 +2455,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.25724601745605</v>
+        <v>28.25724411010742</v>
       </c>
       <c r="C87" t="n">
         <v>38.0099983215332</v>
@@ -2513,7 +2513,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>30.79229164123535</v>
+        <v>30.79228591918945</v>
       </c>
       <c r="C89" t="n">
         <v>41.41999816894531</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>33.05228042602539</v>
+        <v>33.05228424072266</v>
       </c>
       <c r="C90" t="n">
         <v>44.45999908447266</v>
@@ -2571,7 +2571,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>33.23070526123047</v>
+        <v>33.23069763183594</v>
       </c>
       <c r="C91" t="n">
         <v>44.70000076293945</v>
@@ -2629,7 +2629,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>34.53911590576172</v>
+        <v>34.53910064697266</v>
       </c>
       <c r="C93" t="n">
         <v>46.45999908447266</v>
@@ -2658,7 +2658,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.22595977783203</v>
+        <v>36.22597122192383</v>
       </c>
       <c r="C94" t="n">
         <v>48.63000106811523</v>
@@ -2687,7 +2687,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>38.47566604614258</v>
+        <v>38.47566223144531</v>
       </c>
       <c r="C95" t="n">
         <v>51.65000152587891</v>
@@ -2716,7 +2716,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>37.0602912902832</v>
+        <v>37.06029510498047</v>
       </c>
       <c r="C96" t="n">
         <v>49.75</v>
@@ -2745,7 +2745,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>38.10535049438477</v>
+        <v>38.10536193847656</v>
       </c>
       <c r="C97" t="n">
         <v>51.04999923706055</v>
@@ -2774,7 +2774,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>35.79889297485352</v>
+        <v>35.79888916015625</v>
       </c>
       <c r="C98" t="n">
         <v>47.95999908447266</v>
@@ -2803,7 +2803,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>37.14992904663086</v>
+        <v>37.14993286132812</v>
       </c>
       <c r="C99" t="n">
         <v>49.77000045776367</v>
@@ -2861,7 +2861,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>39.75486755371094</v>
+        <v>39.7548828125</v>
       </c>
       <c r="C101" t="n">
         <v>53.13000106811523</v>
@@ -2919,7 +2919,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>40.9329719543457</v>
+        <v>40.9329833984375</v>
       </c>
       <c r="C103" t="n">
         <v>54.58000183105469</v>
@@ -2977,7 +2977,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>42.04293060302734</v>
+        <v>42.04291915893555</v>
       </c>
       <c r="C105" t="n">
         <v>56.06000137329102</v>
@@ -3006,7 +3006,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>40.60473251342773</v>
+        <v>40.60472869873047</v>
       </c>
       <c r="C106" t="n">
         <v>54.02000045776367</v>
@@ -3035,7 +3035,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>40.2664794921875</v>
+        <v>40.26648712158203</v>
       </c>
       <c r="C107" t="n">
         <v>53.56999969482422</v>
@@ -3064,7 +3064,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>41.19103240966797</v>
+        <v>41.19104385375977</v>
       </c>
       <c r="C108" t="n">
         <v>54.79999923706055</v>
@@ -3093,7 +3093,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>42.19745635986328</v>
+        <v>42.19745254516602</v>
       </c>
       <c r="C109" t="n">
         <v>56.0099983215332</v>
@@ -3122,7 +3122,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>36.81822204589844</v>
+        <v>36.8182373046875</v>
       </c>
       <c r="C110" t="n">
         <v>48.86999893188477</v>
@@ -3180,7 +3180,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.37049865722656</v>
+        <v>41.37047958374023</v>
       </c>
       <c r="C112" t="n">
         <v>54.79000091552734</v>
@@ -3209,7 +3209,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>42.50308227539062</v>
+        <v>42.50308990478516</v>
       </c>
       <c r="C113" t="n">
         <v>56.29000091552734</v>
@@ -3238,7 +3238,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>44.25485610961914</v>
+        <v>44.25484848022461</v>
       </c>
       <c r="C114" t="n">
         <v>58.61000061035156</v>
@@ -3267,7 +3267,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>46.77665710449219</v>
+        <v>46.77665328979492</v>
       </c>
       <c r="C115" t="n">
         <v>61.81999969482422</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>45.65679550170898</v>
+        <v>45.65679168701172</v>
       </c>
       <c r="C117" t="n">
         <v>60.34000015258789</v>
@@ -3354,7 +3354,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>43.20002365112305</v>
+        <v>43.20001220703125</v>
       </c>
       <c r="C118" t="n">
         <v>56.81999969482422</v>
@@ -3383,7 +3383,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>47.94426345825195</v>
+        <v>47.94427108764648</v>
       </c>
       <c r="C119" t="n">
         <v>63.06000137329102</v>
@@ -3441,7 +3441,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>47.3242301940918</v>
+        <v>47.32422256469727</v>
       </c>
       <c r="C121" t="n">
         <v>61.97000122070312</v>
@@ -3499,7 +3499,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>38.33589172363281</v>
+        <v>38.33588790893555</v>
       </c>
       <c r="C123" t="n">
         <v>50.20000076293945</v>
@@ -3528,7 +3528,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>41.53362274169922</v>
+        <v>41.53363037109375</v>
       </c>
       <c r="C124" t="n">
         <v>54.04999923706055</v>
@@ -3557,7 +3557,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>42.89374923706055</v>
+        <v>42.89374160766602</v>
       </c>
       <c r="C125" t="n">
         <v>55.81999969482422</v>
@@ -3613,7 +3613,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.87203216552734</v>
+        <v>40.87202453613281</v>
       </c>
       <c r="C127" t="n">
         <v>52.88999938964844</v>
@@ -3667,7 +3667,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>46.23507690429688</v>
+        <v>46.23507308959961</v>
       </c>
       <c r="C129" t="n">
         <v>59.83000183105469</v>
@@ -3696,7 +3696,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>46.10653305053711</v>
+        <v>46.10653686523438</v>
       </c>
       <c r="C130" t="n">
         <v>59.34000015258789</v>
@@ -3725,7 +3725,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>47.94023513793945</v>
+        <v>47.94023132324219</v>
       </c>
       <c r="C131" t="n">
         <v>61.70000076293945</v>
@@ -3812,7 +3812,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>50.17935562133789</v>
+        <v>50.17935943603516</v>
       </c>
       <c r="C134" t="n">
         <v>64.26000213623047</v>
@@ -3868,7 +3868,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>48.99891662597656</v>
+        <v>48.9989013671875</v>
       </c>
       <c r="C136" t="n">
         <v>62.43000030517578</v>
@@ -3895,7 +3895,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>47.80592346191406</v>
+        <v>47.80593490600586</v>
       </c>
       <c r="C137" t="n">
         <v>60.90999984741211</v>
@@ -3951,7 +3951,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>49.31544876098633</v>
+        <v>49.3154296875</v>
       </c>
       <c r="C139" t="n">
         <v>62.52000045776367</v>
@@ -3980,7 +3980,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.62660598754883</v>
+        <v>51.62660217285156</v>
       </c>
       <c r="C140" t="n">
         <v>65.44999694824219</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>47.70630264282227</v>
+        <v>47.706298828125</v>
       </c>
       <c r="C141" t="n">
         <v>60.47999954223633</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>48.68056106567383</v>
+        <v>48.68055725097656</v>
       </c>
       <c r="C142" t="n">
         <v>61.38999938964844</v>
@@ -4067,7 +4067,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.23394012451172</v>
+        <v>51.23392486572266</v>
       </c>
       <c r="C143" t="n">
         <v>64.61000061035156</v>
@@ -4096,7 +4096,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>47.54661178588867</v>
+        <v>47.54661560058594</v>
       </c>
       <c r="C144" t="n">
         <v>59.95999908447266</v>
@@ -4123,7 +4123,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>47.49848175048828</v>
+        <v>47.49848937988281</v>
       </c>
       <c r="C145" t="n">
         <v>59.58000183105469</v>
@@ -4150,7 +4150,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>50.95843124389648</v>
+        <v>50.95842361450195</v>
       </c>
       <c r="C146" t="n">
         <v>63.91999816894531</v>
@@ -4177,7 +4177,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>45.71270370483398</v>
+        <v>45.71269989013672</v>
       </c>
       <c r="C147" t="n">
         <v>57.34000015258789</v>
@@ -4204,7 +4204,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>43.63443374633789</v>
+        <v>43.63442230224609</v>
       </c>
       <c r="C148" t="n">
         <v>54.41999816894531</v>
@@ -4231,7 +4231,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>44.90127944946289</v>
+        <v>44.90128707885742</v>
       </c>
       <c r="C149" t="n">
         <v>56</v>
@@ -4285,7 +4285,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.76271057128906</v>
+        <v>42.76269912719727</v>
       </c>
       <c r="C151" t="n">
         <v>53.02000045776367</v>
@@ -4339,7 +4339,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>42.8836784362793</v>
+        <v>42.88368606567383</v>
       </c>
       <c r="C153" t="n">
         <v>53.16999816894531</v>
@@ -4393,7 +4393,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>33.50557327270508</v>
+        <v>33.50556564331055</v>
       </c>
       <c r="C155" t="n">
         <v>41.29000091552734</v>
@@ -4420,7 +4420,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>35.09604644775391</v>
+        <v>35.09605026245117</v>
       </c>
       <c r="C156" t="n">
         <v>43.25</v>
@@ -4501,7 +4501,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.35711288452148</v>
+        <v>35.35710906982422</v>
       </c>
       <c r="C159" t="n">
         <v>43.20000076293945</v>
@@ -4528,7 +4528,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.50196075439453</v>
+        <v>35.5019645690918</v>
       </c>
       <c r="C160" t="n">
         <v>43.06000137329102</v>
@@ -4555,7 +4555,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.2203369140625</v>
+        <v>39.2203254699707</v>
       </c>
       <c r="C161" t="n">
         <v>47.56999969482422</v>
@@ -4609,7 +4609,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>44.19513702392578</v>
+        <v>44.19515228271484</v>
       </c>
       <c r="C163" t="n">
         <v>53.27999877929688</v>
@@ -4636,7 +4636,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>46.44305801391602</v>
+        <v>46.44305419921875</v>
       </c>
       <c r="C164" t="n">
         <v>55.9900016784668</v>
@@ -4663,7 +4663,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>43.16658020019531</v>
+        <v>43.16657257080078</v>
       </c>
       <c r="C165" t="n">
         <v>52.04000091552734</v>
@@ -4690,7 +4690,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>46.46203231811523</v>
+        <v>46.46202087402344</v>
       </c>
       <c r="C166" t="n">
         <v>55.70000076293945</v>
@@ -4744,7 +4744,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>43.92621231079102</v>
+        <v>43.92621994018555</v>
       </c>
       <c r="C168" t="n">
         <v>52.65999984741211</v>
@@ -4773,7 +4773,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>43.08672332763672</v>
+        <v>43.08673477172852</v>
       </c>
       <c r="C169" t="n">
         <v>51.33000183105469</v>
@@ -4802,7 +4802,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>42.18855667114258</v>
+        <v>42.18856048583984</v>
       </c>
       <c r="C170" t="n">
         <v>50.2599983215332</v>
@@ -4831,7 +4831,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>35.38936996459961</v>
+        <v>35.38937377929688</v>
       </c>
       <c r="C171" t="n">
         <v>42.15999984741211</v>
@@ -4860,7 +4860,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>20.61255264282227</v>
+        <v>20.61255836486816</v>
       </c>
       <c r="C172" t="n">
         <v>24.25</v>
@@ -4889,7 +4889,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>21.61555862426758</v>
+        <v>21.61555671691895</v>
       </c>
       <c r="C173" t="n">
         <v>25.43000030517578</v>
@@ -4918,7 +4918,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>25.55106925964355</v>
+        <v>25.55107307434082</v>
       </c>
       <c r="C174" t="n">
         <v>30.05999946594238</v>
@@ -4947,7 +4947,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>26.77411651611328</v>
+        <v>26.77411460876465</v>
       </c>
       <c r="C175" t="n">
         <v>31.18000030517578</v>
@@ -5005,7 +5005,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>25.02237510681152</v>
+        <v>25.02238082885742</v>
       </c>
       <c r="C177" t="n">
         <v>29.13999938964844</v>
@@ -5032,7 +5032,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>23.90429306030273</v>
+        <v>23.9042911529541</v>
       </c>
       <c r="C178" t="n">
         <v>27.53000068664551</v>
@@ -5086,7 +5086,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>33.37743377685547</v>
+        <v>33.37743759155273</v>
       </c>
       <c r="C180" t="n">
         <v>38.43999862670898</v>
@@ -5113,7 +5113,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>33.14088821411133</v>
+        <v>33.14088439941406</v>
       </c>
       <c r="C181" t="n">
         <v>37.86000061035156</v>
@@ -5194,7 +5194,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>40.71908187866211</v>
+        <v>40.71908569335938</v>
       </c>
       <c r="C184" t="n">
         <v>46.20999908447266</v>
@@ -5221,7 +5221,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>42.69291687011719</v>
+        <v>42.69291305541992</v>
       </c>
       <c r="C185" t="n">
         <v>48.45000076293945</v>
@@ -5248,7 +5248,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>46.56127166748047</v>
+        <v>46.56128311157227</v>
       </c>
       <c r="C186" t="n">
         <v>52.84000015258789</v>
@@ -5275,7 +5275,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>42.20352554321289</v>
+        <v>42.20352935791016</v>
       </c>
       <c r="C187" t="n">
         <v>47.59999847412109</v>
@@ -5302,7 +5302,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>41.98188018798828</v>
+        <v>41.98186874389648</v>
       </c>
       <c r="C188" t="n">
         <v>47.34999847412109</v>
@@ -5329,7 +5329,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>48.37446594238281</v>
+        <v>48.37447357177734</v>
       </c>
       <c r="C189" t="n">
         <v>54.56000137329102</v>
@@ -5387,7 +5387,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>52.70073699951172</v>
+        <v>52.70073318481445</v>
       </c>
       <c r="C191" t="n">
         <v>59.09000015258789</v>
@@ -5416,7 +5416,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>46.91247177124023</v>
+        <v>46.91247940063477</v>
       </c>
       <c r="C192" t="n">
         <v>52.59999847412109</v>
@@ -5474,7 +5474,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>51.80892181396484</v>
+        <v>51.80893325805664</v>
       </c>
       <c r="C194" t="n">
         <v>57.75</v>
@@ -5503,7 +5503,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>54.93989944458008</v>
+        <v>54.93989562988281</v>
       </c>
       <c r="C195" t="n">
         <v>61.2400016784668</v>
@@ -5561,7 +5561,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>52.77920150756836</v>
+        <v>52.77920913696289</v>
       </c>
       <c r="C197" t="n">
         <v>58.5099983215332</v>
@@ -5619,7 +5619,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>46.40751266479492</v>
+        <v>46.40752029418945</v>
       </c>
       <c r="C199" t="n">
         <v>51.13000106811523</v>
@@ -5648,7 +5648,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>46.98840713500977</v>
+        <v>46.9884033203125</v>
       </c>
       <c r="C200" t="n">
         <v>51.77000045776367</v>
@@ -5677,7 +5677,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>46.97024917602539</v>
+        <v>46.97025680541992</v>
       </c>
       <c r="C201" t="n">
         <v>51.75</v>
@@ -5793,7 +5793,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>58.03208541870117</v>
+        <v>58.03208160400391</v>
       </c>
       <c r="C205" t="n">
         <v>63.2400016784668</v>
@@ -5822,7 +5822,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>58.01373291015625</v>
+        <v>58.01373672485352</v>
       </c>
       <c r="C206" t="n">
         <v>63.22000122070312</v>
@@ -5880,7 +5880,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>46.52318572998047</v>
+        <v>46.52317810058594</v>
       </c>
       <c r="C208" t="n">
         <v>50.36000061035156</v>
@@ -5909,7 +5909,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>48.99900436401367</v>
+        <v>48.99899673461914</v>
       </c>
       <c r="C209" t="n">
         <v>53.04000091552734</v>
@@ -5967,7 +5967,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>53.50107955932617</v>
+        <v>53.50107574462891</v>
       </c>
       <c r="C211" t="n">
         <v>57.54000091552734</v>
@@ -5996,7 +5996,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>56.04875183105469</v>
+        <v>56.04874420166016</v>
       </c>
       <c r="C212" t="n">
         <v>60.27999877929688</v>
@@ -6025,7 +6025,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>54.41228485107422</v>
+        <v>54.41229248046875</v>
       </c>
       <c r="C213" t="n">
         <v>58.52000045776367</v>
@@ -6083,7 +6083,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>57.34683990478516</v>
+        <v>57.34683609008789</v>
       </c>
       <c r="C215" t="n">
         <v>61.31000137329102</v>
@@ -6112,7 +6112,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>61.55595016479492</v>
+        <v>61.55594635009766</v>
       </c>
       <c r="C216" t="n">
         <v>65.80999755859375</v>
@@ -6141,7 +6141,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>63.71315383911133</v>
+        <v>63.71315765380859</v>
       </c>
       <c r="C217" t="n">
         <v>67.75</v>
@@ -6170,7 +6170,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>65.36829376220703</v>
+        <v>65.3682861328125</v>
       </c>
       <c r="C218" t="n">
         <v>69.51000213623047</v>
@@ -6199,7 +6199,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>68.54689025878906</v>
+        <v>68.54686737060547</v>
       </c>
       <c r="C219" t="n">
         <v>72.88999938964844</v>
@@ -6228,7 +6228,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>73.86266326904297</v>
+        <v>73.8626708984375</v>
       </c>
       <c r="C220" t="n">
         <v>78.16999816894531</v>
@@ -6286,7 +6286,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>74.47684478759766</v>
+        <v>74.47683715820312</v>
       </c>
       <c r="C222" t="n">
         <v>78.81999969482422</v>
@@ -6315,7 +6315,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>70.52987670898438</v>
+        <v>70.52988433837891</v>
       </c>
       <c r="C223" t="n">
         <v>74.23999786376953</v>
@@ -6344,7 +6344,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>75.27052307128906</v>
+        <v>75.27051544189453</v>
       </c>
       <c r="C224" t="n">
         <v>79.23000335693359</v>
@@ -6373,7 +6373,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>73.19945526123047</v>
+        <v>73.19947052001953</v>
       </c>
       <c r="C225" t="n">
         <v>77.05000305175781</v>
@@ -6400,7 +6400,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>69.95310211181641</v>
+        <v>69.95309448242188</v>
       </c>
       <c r="C226" t="n">
         <v>73.23000335693359</v>
@@ -6427,7 +6427,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>72.48451232910156</v>
+        <v>72.48450469970703</v>
       </c>
       <c r="C227" t="n">
         <v>75.87999725341797</v>
@@ -6454,7 +6454,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>73.43977355957031</v>
+        <v>73.43975830078125</v>
       </c>
       <c r="C228" t="n">
         <v>76.87999725341797</v>
@@ -6508,7 +6508,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>70.75222015380859</v>
+        <v>70.75222778320312</v>
       </c>
       <c r="C230" t="n">
         <v>73.66000366210938</v>
@@ -6562,7 +6562,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>83.9117431640625</v>
+        <v>83.91175079345703</v>
       </c>
       <c r="C232" t="n">
         <v>86.94000244140625</v>
@@ -6643,7 +6643,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>83.0443115234375</v>
+        <v>83.04431915283203</v>
       </c>
       <c r="C235" t="n">
         <v>85.58999633789062</v>
@@ -6755,7 +6755,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>77.06169128417969</v>
+        <v>77.06169891357422</v>
       </c>
       <c r="C239" t="n">
         <v>78.95999908447266</v>
@@ -6784,7 +6784,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>74.32901763916016</v>
+        <v>74.32901000976562</v>
       </c>
       <c r="C240" t="n">
         <v>76.16000366210938</v>
